--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486875_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486875_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1956</v>
+        <v>6.7137</v>
       </c>
       <c r="E2" t="n">
-        <v>8.5527</v>
+        <v>7.9522</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.3571</v>
+        <v>-1.2385</v>
       </c>
       <c r="G2" t="n">
         <v>5.5552</v>
@@ -610,13 +610,13 @@
         <v>1.4374</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9895</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5147</v>
+        <v>0.9142</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5252</v>
+        <v>-0.4066</v>
       </c>
       <c r="V2" t="n">
         <v>0.2402</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.2499</v>
+        <v>5.17</v>
       </c>
       <c r="E3" t="n">
-        <v>8.0383</v>
+        <v>6.8102</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.7884</v>
+        <v>-1.6402</v>
       </c>
       <c r="G3" t="n">
         <v>5.2395</v>
@@ -688,13 +688,13 @@
         <v>0.8214</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5012</v>
+        <v>0.4214</v>
       </c>
       <c r="T3" t="n">
-        <v>3.0257</v>
+        <v>1.7976</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.5244</v>
+        <v>-1.3762</v>
       </c>
       <c r="V3" t="n">
         <v>1.7679</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1726</v>
+        <v>3.9599</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3811</v>
+        <v>3.9313</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2085</v>
+        <v>0.0286</v>
       </c>
       <c r="G4" t="n">
         <v>3.9978</v>
@@ -766,13 +766,13 @@
         <v>0.8214</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5315</v>
+        <v>0.2558</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0541</v>
+        <v>0.6042</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5856</v>
+        <v>-0.3485</v>
       </c>
       <c r="V4" t="n">
         <v>0.9384</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. LOPEZ-SANVICENTE RETA</t>
+          <t>H. FIGUEROA ÁLVAREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0574</v>
+        <v>3.7041</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2507</v>
+        <v>4.9287</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8067</v>
+        <v>-1.2246</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5765</v>
+        <v>3.4735</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2691</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>2.3074</v>
+        <v>3.399</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4678</v>
+        <v>4.6301</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6263</v>
+        <v>0.5129</v>
       </c>
       <c r="L5" t="n">
-        <v>1.8415</v>
+        <v>4.1171</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1087</v>
+        <v>-1.1566</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3572</v>
+        <v>-0.4385</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4659</v>
+        <v>-0.7181</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.616</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0267</v>
+        <v>1.6427</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4809</v>
+        <v>-0.6257</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8096</v>
+        <v>0.4958</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3287</v>
+        <v>-1.1215</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.8295</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. FIGUEROA ÁLVAREZ</t>
+          <t>P. LOPEZ-SANVICENTE RETA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5189</v>
+        <v>2.5039</v>
       </c>
       <c r="E6" t="n">
-        <v>3.9214</v>
+        <v>1.964</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4024</v>
+        <v>0.5399</v>
       </c>
       <c r="G6" t="n">
-        <v>3.4735</v>
+        <v>2.5765</v>
       </c>
       <c r="H6" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.2691</v>
       </c>
       <c r="I6" t="n">
-        <v>3.399</v>
+        <v>2.3074</v>
       </c>
       <c r="J6" t="n">
-        <v>4.6301</v>
+        <v>2.4678</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5129</v>
+        <v>0.6263</v>
       </c>
       <c r="L6" t="n">
-        <v>4.1171</v>
+        <v>1.8415</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1566</v>
+        <v>0.1087</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4385</v>
+        <v>-0.3572</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7181</v>
+        <v>0.4659</v>
       </c>
       <c r="P6" t="n">
-        <v>0.616</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6427</v>
+        <v>1.0267</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.8108</v>
+        <v>-0.0726</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5115</v>
+        <v>0.5229</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.2993</v>
+        <v>-0.5955</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8295</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5893</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. FRITZ</t>
+          <t>G. VAZQUEZ VALLEJO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.0117</v>
+        <v>1.6969</v>
       </c>
       <c r="E7" t="n">
-        <v>3.4886</v>
+        <v>2.7835</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4769</v>
+        <v>-1.0866</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9907</v>
+        <v>1.6843</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5906</v>
+        <v>0.603</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5813</v>
+        <v>1.0813</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9657</v>
+        <v>1.9382</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5713</v>
+        <v>1.3466</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3943</v>
+        <v>0.5916</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.975</v>
+        <v>-0.2539</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1619</v>
+        <v>-0.7435</v>
       </c>
       <c r="O7" t="n">
-        <v>0.187</v>
+        <v>0.4897</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8214</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8214</v>
+        <v>0.2053</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1495</v>
+        <v>-0.3447</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9336</v>
+        <v>0.6934</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0831</v>
+        <v>-1.0381</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3491</v>
+        <v>1.1786</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5893</v>
+        <v>1.1786</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. VAZQUEZ VALLEJO</t>
+          <t>J. FRITZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.108</v>
+        <v>1.5859</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1946</v>
+        <v>3.2407</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0866</v>
+        <v>-1.6548</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6843</v>
+        <v>0.9907</v>
       </c>
       <c r="H8" t="n">
-        <v>0.603</v>
+        <v>-0.5906</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0813</v>
+        <v>1.5813</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9382</v>
+        <v>1.9657</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3466</v>
+        <v>0.5713</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5916</v>
+        <v>1.3943</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2539</v>
+        <v>-0.975</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7435</v>
+        <v>-1.1619</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4897</v>
+        <v>0.187</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.8214</v>
+        <v>0.8214</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2053</v>
+        <v>0.8214</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9336</v>
+        <v>-0.5753</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1045</v>
+        <v>0.6857</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0381</v>
+        <v>-1.2609</v>
       </c>
       <c r="V8" t="n">
-        <v>1.1786</v>
+        <v>0.3491</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1786</v>
+        <v>0.5893</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2452</v>
+        <v>0.0142</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0703</v>
+        <v>1.2408</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3155</v>
+        <v>-1.2266</v>
       </c>
       <c r="G9" t="n">
         <v>1.3422</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1069</v>
+        <v>-0.8475</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3294</v>
+        <v>-0.1589</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7775</v>
+        <v>-0.6886</v>
       </c>
       <c r="V9" t="n">
         <v>-0.4805</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. GALLEGO BROTO</t>
+          <t>A. BADMUS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.407</v>
+        <v>-1.3055</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1317</v>
+        <v>-1.845</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2753</v>
+        <v>0.5394</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2238</v>
+        <v>-0.1173</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0843</v>
+        <v>-0.3989</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1395</v>
+        <v>0.2816</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.7603</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-0.2394</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.9997</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2238</v>
+        <v>-0.8776</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0843</v>
+        <v>-0.1596</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1395</v>
+        <v>-0.7181</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.0267</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2119</v>
+        <v>0.2964</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1317</v>
+        <v>0.6042</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.08019999999999999</v>
+        <v>-0.3078</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.4189</v>
+        <v>-0.4579</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-1.1561</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.4189</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O. THIAM PEDRERA</t>
+          <t>P. GALLEGO BROTO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6809</v>
+        <v>-1.3181</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6851</v>
+        <v>-0.1317</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3659</v>
+        <v>-1.1864</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1261</v>
+        <v>0.2238</v>
       </c>
       <c r="H11" t="n">
-        <v>1.1027</v>
+        <v>0.0843</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.2288</v>
+        <v>0.1395</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2435</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>2.1252</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.8817</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3696</v>
+        <v>0.2238</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0225</v>
+        <v>0.0843</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3472</v>
+        <v>0.1395</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4107</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4107</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6937</v>
+        <v>-0.123</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4416</v>
+        <v>-0.1317</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2521</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.6591</v>
+        <v>-1.4189</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.6591</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. BADMUS</t>
+          <t>O. THIAM PEDRERA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0335</v>
+        <v>-1.7894</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3951</v>
+        <v>1.1694</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3616</v>
+        <v>-2.9588</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1173</v>
+        <v>-1.1261</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3989</v>
+        <v>1.1027</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2816</v>
+        <v>-2.2288</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7603</v>
+        <v>0.2435</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2394</v>
+        <v>2.1252</v>
       </c>
       <c r="L12" t="n">
-        <v>0.9997</v>
+        <v>-1.8817</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8776</v>
+        <v>-1.3696</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1596</v>
+        <v>-1.0225</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7181</v>
+        <v>-0.3472</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.0267</v>
+        <v>0.4107</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.0267</v>
+        <v>0.4107</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4316</v>
+        <v>0.5851</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0541</v>
+        <v>0.9258999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4857</v>
+        <v>-0.3408</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.4579</v>
+        <v>-1.6591</v>
       </c>
       <c r="W12" t="n">
-        <v>-1.1561</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.6982</v>
+        <v>-1.6591</v>
       </c>
     </row>
     <row r="13">
@@ -1423,25 +1423,25 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>19.9475</v>
+        <v>20.9356</v>
       </c>
       <c r="E13" t="n">
-        <v>31.056</v>
+        <v>32.0441</v>
       </c>
       <c r="F13" t="n">
-        <v>-11.1083</v>
+        <v>-11.1086</v>
       </c>
       <c r="G13" t="n">
         <v>23.8401</v>
       </c>
       <c r="H13" t="n">
-        <v>4.344599999999999</v>
+        <v>4.3446</v>
       </c>
       <c r="I13" t="n">
         <v>19.4954</v>
       </c>
       <c r="J13" t="n">
-        <v>30.57780000000001</v>
+        <v>30.5778</v>
       </c>
       <c r="K13" t="n">
         <v>10.4001</v>
@@ -1453,7 +1453,7 @@
         <v>-6.7377</v>
       </c>
       <c r="N13" t="n">
-        <v>-6.055600000000001</v>
+        <v>-6.0556</v>
       </c>
       <c r="O13" t="n">
         <v>-0.6821999999999999</v>
@@ -1468,16 +1468,16 @@
         <v>8.213699999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5105</v>
+        <v>-0.5225000000000002</v>
       </c>
       <c r="T13" t="n">
-        <v>5.965299999999999</v>
+        <v>6.953299999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-7.475699999999998</v>
+        <v>-7.4758</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6980000000000004</v>
+        <v>0.698</v>
       </c>
       <c r="W13" t="n">
         <v>5.806700000000001</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>O. NDOUR</t>
+          <t>A. LIBROIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1222</v>
+        <v>2.7223</v>
       </c>
       <c r="E14" t="n">
-        <v>2.594</v>
+        <v>5.5526</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4718</v>
+        <v>-2.8303</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6893</v>
+        <v>1.7092</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1419</v>
+        <v>-1.2063</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.8311</v>
+        <v>2.9155</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3676</v>
+        <v>5.4598</v>
       </c>
       <c r="K14" t="n">
-        <v>1.9466</v>
+        <v>0.04</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.579</v>
+        <v>5.4198</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.0569</v>
+        <v>-3.7506</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8047</v>
+        <v>-1.2462</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.2522</v>
+        <v>-2.5044</v>
       </c>
       <c r="P14" t="n">
-        <v>1.0267</v>
+        <v>0.8214</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R14" t="n">
-        <v>1.0267</v>
+        <v>1.8481</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1811</v>
+        <v>0.4319</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6227</v>
+        <v>0.8792</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4416</v>
+        <v>-0.4473</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.3963</v>
+        <v>-0.2402</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.3963</v>
+        <v>0.2402</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K. OBIEKWE SAM</t>
+          <t>A. SANCHEZ PERDIGUERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0974</v>
+        <v>0.8148</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7687</v>
+        <v>2.6103</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6713</v>
+        <v>-1.7956</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7151999999999999</v>
+        <v>-1.7542</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9308999999999999</v>
+        <v>1.7555</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2157</v>
+        <v>-3.5098</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3276</v>
+        <v>1.5994</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9855</v>
+        <v>2.8362</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6579</v>
+        <v>-1.2368</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6124000000000001</v>
+        <v>-3.3536</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0546</v>
+        <v>-1.0807</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4422</v>
+        <v>-2.2729</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2053</v>
+        <v>1.6427</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8214</v>
+        <v>1.6427</v>
       </c>
       <c r="S15" t="n">
-        <v>2.0064</v>
+        <v>0.8174</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4678</v>
+        <v>1.011</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4614</v>
+        <v>-0.1936</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.4189</v>
+        <v>0.1088</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4189</v>
+        <v>0.1088</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. LIBROIA</t>
+          <t>R. UKAWUBA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9056999999999999</v>
+        <v>0.4514</v>
       </c>
       <c r="E16" t="n">
-        <v>4.1927</v>
+        <v>3.7687</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.2871</v>
+        <v>-3.3174</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7092</v>
+        <v>-3.2662</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.2063</v>
+        <v>-0.6062</v>
       </c>
       <c r="I16" t="n">
-        <v>2.9155</v>
+        <v>-2.6599</v>
       </c>
       <c r="J16" t="n">
-        <v>5.4598</v>
+        <v>-0.5303</v>
       </c>
       <c r="K16" t="n">
-        <v>0.04</v>
+        <v>0.0881</v>
       </c>
       <c r="L16" t="n">
-        <v>5.4198</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.7506</v>
+        <v>-2.7358</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2462</v>
+        <v>-0.6943</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.5044</v>
+        <v>-2.0415</v>
       </c>
       <c r="P16" t="n">
-        <v>0.8214</v>
+        <v>0.4107</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8481</v>
+        <v>0.4107</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3847</v>
+        <v>0.3603</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4806</v>
+        <v>0.5229</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9041</v>
+        <v>-0.1626</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2402</v>
+        <v>2.9466</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2402</v>
+        <v>3.7761</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.4805</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. UKAWUBA</t>
+          <t>K. OBIEKWE SAM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7302999999999999</v>
+        <v>-0.292</v>
       </c>
       <c r="E17" t="n">
-        <v>4.1871</v>
+        <v>1.4089</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.4568</v>
+        <v>-1.7009</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.2662</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6062</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.6599</v>
+        <v>-0.2157</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5303</v>
+        <v>1.3276</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0881</v>
+        <v>1.9855</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.6579</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.7358</v>
+        <v>-0.6124000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6943</v>
+        <v>-1.0546</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.0415</v>
+        <v>0.4422</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4107</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4107</v>
+        <v>0.8214</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6392</v>
+        <v>0.6169</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9413</v>
+        <v>1.1079</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3021</v>
+        <v>-0.491</v>
       </c>
       <c r="V17" t="n">
-        <v>2.9466</v>
+        <v>-1.4189</v>
       </c>
       <c r="W17" t="n">
-        <v>3.7761</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.8295</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. SANCHEZ PERDIGUERO</t>
+          <t>O. NDOUR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6893</v>
+        <v>-0.3422</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5057</v>
+        <v>1.1296</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8165</v>
+        <v>-1.4718</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.7542</v>
+        <v>-0.6893</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7555</v>
+        <v>1.1419</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.5098</v>
+        <v>-1.8311</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5994</v>
+        <v>1.3676</v>
       </c>
       <c r="K18" t="n">
-        <v>2.8362</v>
+        <v>1.9466</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2368</v>
+        <v>-0.579</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.3536</v>
+        <v>-2.0569</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0807</v>
+        <v>-0.8047</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.2729</v>
+        <v>-1.2522</v>
       </c>
       <c r="P18" t="n">
-        <v>1.6427</v>
+        <v>1.0267</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6427</v>
+        <v>1.0267</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6919</v>
+        <v>0.7167</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9064</v>
+        <v>1.1583</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2145</v>
+        <v>-0.4416</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1088</v>
+        <v>-1.3963</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-1.3963</v>
       </c>
       <c r="X18" t="n">
-        <v>0.1088</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9375</v>
+        <v>-1.6951</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7389</v>
+        <v>1.6343</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.6763</v>
+        <v>-3.3294</v>
       </c>
       <c r="G19" t="n">
         <v>-2.2819</v>
@@ -1936,13 +1936,13 @@
         <v>0.8214</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3886</v>
+        <v>-0.1463</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9413</v>
+        <v>0.8367</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.33</v>
+        <v>-0.983</v>
       </c>
       <c r="V19" t="n">
         <v>0.9384</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2703</v>
+        <v>-2.2633</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0742</v>
+        <v>0.1788</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.3445</v>
+        <v>-2.4421</v>
       </c>
       <c r="G20" t="n">
         <v>-1.9495</v>
@@ -2014,13 +2014,13 @@
         <v>0.8214</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1154</v>
+        <v>-0.1085</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1781</v>
+        <v>0.2827</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2935</v>
+        <v>-0.3912</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3269</v>
+        <v>-2.9033</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1404</v>
+        <v>-0.8266</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1865</v>
+        <v>-2.0767</v>
       </c>
       <c r="G21" t="n">
         <v>-3.6791</v>
@@ -2092,13 +2092,13 @@
         <v>0.616</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.504</v>
+        <v>-0.0804</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1822</v>
+        <v>0.1316</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3219</v>
+        <v>-0.2121</v>
       </c>
       <c r="V21" t="n">
         <v>0.2402</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0043</v>
+        <v>-3.408</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5057</v>
+        <v>-1.0873</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.4986</v>
+        <v>-2.3208</v>
       </c>
       <c r="G22" t="n">
         <v>-2.2778</v>
@@ -2170,13 +2170,13 @@
         <v>0.616</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1372</v>
+        <v>0.4591</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0232</v>
+        <v>0.4416</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1604</v>
+        <v>0.0175</v>
       </c>
       <c r="V22" t="n">
         <v>-1.1786</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L. SOUMBEY-ALLEY</t>
+          <t>A. HARO VAL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.4361</v>
+        <v>-5.2881</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2101</v>
+        <v>-2.1553</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.2261</v>
+        <v>-3.1328</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.2537</v>
+        <v>-5.1127</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.6861</v>
+        <v>-2.608</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.5676</v>
+        <v>-2.5047</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5981</v>
+        <v>-1.7561</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.4398</v>
+        <v>-1.6638</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.1582</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-4.6556</v>
+        <v>-3.3566</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.2462</v>
+        <v>-0.9442</v>
       </c>
       <c r="O23" t="n">
-        <v>-3.4094</v>
+        <v>-2.4124</v>
       </c>
       <c r="P23" t="n">
         <v>-0.2053</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8481</v>
+        <v>0.8214</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2789</v>
+        <v>0.03</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3717</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6506</v>
+        <v>-0.5975</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6982</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0698</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.7679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. HARO VAL</t>
+          <t>L. SOUMBEY-ALLEY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.5172</v>
+        <v>-6.349</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0968</v>
+        <v>-1.1055</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.4204</v>
+        <v>-5.2436</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.1127</v>
+        <v>-5.2537</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.608</v>
+        <v>-1.6861</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.5047</v>
+        <v>-3.5676</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.7561</v>
+        <v>-0.5981</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.6638</v>
+        <v>-0.4398</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.1582</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.3566</v>
+        <v>-4.6556</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.9442</v>
+        <v>-1.2462</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.4124</v>
+        <v>-3.4094</v>
       </c>
       <c r="P24" t="n">
         <v>-0.2053</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R24" t="n">
-        <v>0.8214</v>
+        <v>1.8481</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1991</v>
+        <v>-0.1918</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3139</v>
+        <v>0.4763</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8852</v>
+        <v>-0.6681</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.6982</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.0698</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.7679</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-19.9474</v>
+        <v>-18.5525</v>
       </c>
       <c r="E25" t="n">
-        <v>11.1083</v>
+        <v>11.1085</v>
       </c>
       <c r="F25" t="n">
-        <v>-31.0559</v>
+        <v>-29.6614</v>
       </c>
       <c r="G25" t="n">
         <v>-23.84</v>
@@ -2377,13 +2377,13 @@
         <v>-19.4953</v>
       </c>
       <c r="J25" t="n">
-        <v>6.7377</v>
+        <v>6.737700000000001</v>
       </c>
       <c r="K25" t="n">
         <v>6.055699999999998</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6821000000000002</v>
+        <v>0.6821000000000007</v>
       </c>
       <c r="M25" t="n">
         <v>-30.5776</v>
@@ -2395,7 +2395,7 @@
         <v>-20.1775</v>
       </c>
       <c r="P25" t="n">
-        <v>3.0803</v>
+        <v>3.080300000000001</v>
       </c>
       <c r="Q25" t="n">
         <v>-8.2136</v>
@@ -2404,16 +2404,16 @@
         <v>11.2939</v>
       </c>
       <c r="S25" t="n">
-        <v>1.5107</v>
+        <v>2.9053</v>
       </c>
       <c r="T25" t="n">
-        <v>7.4758</v>
+        <v>7.4757</v>
       </c>
       <c r="U25" t="n">
-        <v>-5.9653</v>
+        <v>-4.5705</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.6982000000000003</v>
+        <v>-0.6982</v>
       </c>
       <c r="W25" t="n">
         <v>5.1086</v>
